--- a/out/RQ2_architecture_metrics/rq2_fallback_answers_joined.xlsx
+++ b/out/RQ2_architecture_metrics/rq2_fallback_answers_joined.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -891,210 +891,10 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>p24</t>
+          <t>p31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
-        <is>
-          <t>Create a profile to test a bike shop’s virtual assistant. The user should be a customer interacting in English who is looking for general information about the shop and its standard services. During the interaction, the user should ask about the opening and closing times of the bike shop, the price of a new bike tire, the price of a standard bike tune-up, and the price of a new bike seat. In addition, the user should ask for general advice on how to properly take care of a bike, focusing on basic maintenance and good practices rather than advanced repairs. The user must behave like a normal customer and phrase questions clearly and directly. The user should not ask about appointments, specific bike models, custom or advanced repairs, warranties, delivery services, or any topic outside of basic pricing, shop hours, and general bike care. This profile is intended to test whether the chatbot provides accurate and relevant information for each request, uses appropriate bike-shop terminology, clearly states prices, and avoids introducing unrelated services or unsolicited suggestions.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>I've loaded the relevant documentation for creating profiles from the `sensei-chat-guide.md`. Now, I'll create a profile for the bike shop's virtual assistant based on your specifications.
-### Profile Structure
-The profile will include:
-- **Test Name**: A descriptive name for the profile.
-- **LLM Settings**: Configuration for the language model.
-- **User Details**: Language, role, context, and goals.
-- **Chatbot Interaction**: Details about the chatbot's behavior and expected outputs.
-- **Conversation Controls**: How many interactions to simulate and the style of interaction.
-### YAML Profile for Bike Shop Virtual Assistant
-Here's the proposed profile:
-```yaml
-test_name: "bike_shop_virtual_assistant"
-llm:
-  temperature: 0.7
-  model: gpt-4
-  model_prov: openai
-  format:
-    type: text
-user:
-  language: English
-  role: "A customer seeking general information about the bike shop and its services."
-  context:
-    - "The user is interested in shop hours, pricing for services, and basic bike maintenance."
-  goals:
-    - "What are the opening and closing times of the bike shop?"
-    - "How much does a new bike tire cost?"
-    - "What is the price for a standard bike tune-up?"
-    - "How much is a new bike seat?"
-    - "Can you give me some general advice on how to take care of my bike?"
-chatbot:
-  is_starter: true
-  fallback: "I'm sorry, I can't help with that."
-  output:
-    - opening_hours:
-        type: string
-        description: "The opening and closing times of the bike shop."
-    - tire_price:
-        type: currency
-        description: "The price of a new bike tire."
-    - tune_up_price:
-        type: currency
-        description: "The price of a standard bike tune-up."
-    - seat_price:
-        type: currency
-        description: "The price of a new bike seat."
-    - maintenance_advice:
-        type: string
-        description: "General advice on bike maintenance."
-conversation:
-  number: 5
-  goal_style:
-    steps: 5
-  interaction_style:
-    - single questions
-```
-### Summary of the Profile
-- **Purpose**: To test the bike shop's virtual assistant by simulating a customer asking about shop hours, pricing, and basic bike maintenance.
-- **Outputs**: The profile specifies what information should be extracted from the chatbot's responses, ensuring that the chatbot provides accurate and relevant information.
-Would you like to proceed with this profile, or do you have any adjustments or additional requirements? 😊</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Sure! Here’s a profile designed to test a bike shop’s virtual assistant, focusing on general information and standard services. This profile will ensure the user behaves like a normal customer, asking clear and direct questions. 
-```yaml
-test_name: "bike_shop_general_information"
-llm:
-  temperature: 0.5
-  model: gpt-4o-mini
-  format:
-    type: text
-user:
-  language: English
-  role: "A customer seeking general information about the bike shop and its standard services."
-  context:
-    - "You want to gather basic information about the shop's services and operating hours."
-    - "You are interested in understanding pricing for common items and maintenance advice."
-  goals:
-    - "What are the opening and closing times of the bike shop?"
-    - "How much does a new bike tire cost?"
-    - "What is the price of a standard bike tune-up?"
-    - "How much is a new bike seat?"
-    - "Can you give me some general advice on how to properly take care of my bike?"
-chatbot:
-  is_starter: true
-  fallback: "I'm sorry, it's a little loud in my shop, can you say that again?"
-  output:
-    - opening_and_closing_times:
-        type: string
-        description: "The opening and closing times of the bike shop."
-    - tire_price:
-        type: money
-        description: "The price of a new bike tire."
-    - tune_up_price:
-        type: money
-        description: "The price of a standard bike tune-up."
-    - seat_price:
-        type: money
-        description: "The price of a new bike seat."
-    - maintenance_advice:
-        type: string
-        description: "General advice on how to properly take care of a bike."
-conversation:
-  number: 5
-  goal_style:
-    all_answered:
-      export: true
-      limit: 5
-  interaction_style:
-    - default
-```
-### Explanation:
-- **User Role**: The user is defined as a customer looking for basic information, ensuring they ask clear and direct questions.
-- **Goals**: The goals specify the exact questions the user will ask, focusing on shop hours, pricing for standard items, and basic maintenance advice.
-- **Chatbot Output**: The expected outputs are clearly defined to ensure the chatbot provides relevant information.
-- **Conversation Control**: The conversation is set to allow for a maximum of 5 interactions, ensuring all goals can be addressed.
-Feel free to modify any part of this profile to better suit your testing needs! Happy testing! 😊</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>That sounds like a great profile to create! Here’s a YAML profile that captures all your requirements for testing the bike shop’s virtual assistant. This profile defines the user’s context, goals, and the expected interaction style. Let’s dive in! 😊
-```yaml
-test_name: "Bike Shop Virtual Assistant Inquiry"
-llm:
-  temperature: 0.6
-  model: gpt-4o-mini
-  format:
-    type: text
-user:
-  language: English
-  role: "A customer seeking general information about the bike shop and its standard services."
-  context:
-    - "You are looking for basic information about the bike shop's services."
-    - "You want to know about shop hours, pricing for standard items, and basic bike maintenance."
-  goals:
-    - "What are the opening and closing times of the bike shop?"
-    - "How much does a new bike tire cost?"
-    - "What is the price of a standard bike tune-up?"
-    - "How much is a new bike seat?"
-    - "Can you provide general advice on how to properly take care of a bike?"
-conversation:
-  number: 5
-  goal_style:
-    all_answered:
-      export: true
-      limit: 5
-  interaction_style:
-    - default
-chatbot:
-  is_starter: false
-  fallback: "I'm sorry, could you repeat that?"
-  output:
-    - opening_and_closing_time:
-        type: string
-        description: "The shop's operating hours."
-    - tire_price:
-        type: money
-        description: "The price of a new bike tire."
-    - tune_up_price:
-        type: money
-        description: "The price of a standard bike tune-up."
-    - seat_price:
-        type: money
-        description: "The price of a new bike seat."
-    - maintenance_advice:
-        type: string
-        description: "General advice on bike maintenance and care."
-```
-This profile sets up a clear interaction for the user, ensuring they ask relevant questions while avoiding unrelated topics. It also specifies the expected outputs from the chatbot, making it easy to validate the responses. Happy testing! 🚴‍♂️✨</t>
-        </is>
-      </c>
-      <c r="G4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>20260324_134818_560</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>p31</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
         <is>
           <t>Fix this profile: test_name: general_information_seeker
 llm:
@@ -1142,12 +942,12 @@
   - single question</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>I'm sorry, but I tried several times and couldn't finish a version that meets all the requirements. The interaction style needs to be one of the allowed options. If you have any specific preferences, please let me know!</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Sure! Let's tidy up your profile for `general_information_seeker`. It looks like there are some formatting issues and a couple of inconsistencies in the types used. Here’s a revised version:
 ```yaml
@@ -1206,7 +1006,7 @@
 Feel free to adjust any specific details as needed! If you have any more questions or need further assistance, just let me know! 😊</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Sure! It looks like your profile has a few formatting issues and inconsistencies. Here's a corrected version of your `general_information_seeker` profile:
 ```yaml
@@ -1263,28 +1063,28 @@
 Feel free to let me know if you need any more help! 😊</t>
         </is>
       </c>
-      <c r="G5" t="b">
+      <c r="G4" t="b">
         <v>1</v>
       </c>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" t="b">
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>20260324_134818_560</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>p33</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>I have this profile, but I don't know what to add to the chatbot field. Can you help me completing it for me?: test_name: pizza_and_drinks_information_seeker
 llm:
@@ -1318,12 +1118,12 @@
   - single question</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>I'm sorry, but I tried several times and couldn't finish a version that meets all the requirements. The main issue is that the `chatbot` field needs to include some specific details. If you can provide any additional information or examples, I’d be happy to help!</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>I'm really sorry that we couldn't successfully validate your request after three attempts. It seems there was an issue with the 'user.language' field being required, and I understand you were looking to fix your profile. I encourage you to adjust your instructions based on the feedback provided or try rephrasing your request. If you need further assistance, please feel free to reach out again. Thank you for your understanding!
 Validator feedback:
@@ -1336,7 +1136,7 @@
 Keep blocks none unchanged. Rewrite the full reply, but only modify blocks 1 and any prose that references them.</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Absolutely, I’d be happy to help you complete the `chatbot` field for your profile! Since this profile is focused on gathering information about pizzas and drinks, we want to ensure that the `chatbot.output` section captures the relevant details that the chatbot should provide. Here’s a suggestion for your `chatbot` field:
 ```yaml
@@ -1372,39 +1172,39 @@
 Feel free to modify any descriptions or types as needed! 😊</t>
         </is>
       </c>
-      <c r="G6" t="b">
+      <c r="G5" t="b">
         <v>1</v>
       </c>
-      <c r="H6" t="b">
+      <c r="H5" t="b">
         <v>1</v>
       </c>
-      <c r="I6" t="b">
+      <c r="I5" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>20260324_134818_560</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>p49</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>How does the pairwise function work?</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>It seems like you're asking about a specific function or feature, but I need a bit more context to provide an accurate answer. Are you referring to a function in a programming language, a mathematical concept, or something related to SENSEI rules, profiles, or connectors? 
 If it's related to SENSEI, please clarify, and I'll do my best to help! 😊</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>The `pairwise` function in Sensei is a powerful tool used to generate combinations of variables for testing. It ensures that every possible pair of values from two or more variables is covered in your conversations, without creating an overwhelming number of combinations. This is especially useful when you want to test interactions between different inputs efficiently.
 ### How It Works:
@@ -1430,7 +1230,7 @@
 It's a fantastic way to streamline your testing process while still being thorough! If you have any more questions or need further clarification, feel free to ask! 😊</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>The pairwise function in Sensei is a powerful tool for generating combinations of variables in your user profiles. It allows you to efficiently cover all possible pairs of values across multiple variables without having to create every single combination manually. This is particularly useful when you want to test interactions between different inputs while keeping the number of test cases manageable.
 ### How It Works:
@@ -1461,33 +1261,33 @@
 If you have any specific scenarios or questions about how to implement it, feel free to ask! 😊</t>
         </is>
       </c>
-      <c r="G7" t="b">
+      <c r="G6" t="b">
         <v>1</v>
       </c>
-      <c r="H7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7" t="b">
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>20260324_134818_560</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>p50</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>What is an oracle?</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>In the context of SENSEI rules, an **oracle** is a validation condition used to determine whether a specific rule passes or fails based on the outputs of a conversation. It acts as a logical expression that evaluates to either true or false.
 ### Key Points about Oracles:
@@ -1498,12 +1298,12 @@
 If you have any specific questions about how to implement or use oracles in your rules, feel free to ask! 😊</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>I can only help with SENSEI rules, SENSEI profiles, SENSEI connectors, or related explanations. Please share one of those requests.</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>In the context of Sensei and testing, an **oracle** is a mechanism or method used to determine whether the output of a system (like a chatbot) is correct or not. It acts as a reference point for validation.
 In Sensei-check, oracles can be defined in your rules to specify the expected behavior or output of the chatbot based on certain inputs. For example, if you have a rule that checks if the price of a pizza is correct, the oracle would define the condition that determines if that price is valid.
@@ -1511,225 +1311,28 @@
 If you have any specific examples or need help with oracles in your rules, feel free to ask! 😊</t>
         </is>
       </c>
-      <c r="G8" t="b">
-        <v>0</v>
-      </c>
-      <c r="H8" t="b">
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="b">
         <v>1</v>
       </c>
-      <c r="I8" t="b">
+      <c r="I7" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>20260324_144250_084</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>p24</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Create a profile to test a bike shop’s virtual assistant. The user should be a customer interacting in English who is looking for general information about the shop and its standard services. During the interaction, the user should ask about the opening and closing times of the bike shop, the price of a new bike tire, the price of a standard bike tune-up, and the price of a new bike seat. In addition, the user should ask for general advice on how to properly take care of a bike, focusing on basic maintenance and good practices rather than advanced repairs. The user must behave like a normal customer and phrase questions clearly and directly. The user should not ask about appointments, specific bike models, custom or advanced repairs, warranties, delivery services, or any topic outside of basic pricing, shop hours, and general bike care. This profile is intended to test whether the chatbot provides accurate and relevant information for each request, uses appropriate bike-shop terminology, clearly states prices, and avoids introducing unrelated services or unsolicited suggestions.</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Here's the YAML profile for the bike shop's virtual assistant:
-```yaml
-test_name: "Bike Shop Virtual Assistant Test"
-llm:
-  temperature: 0.7
-  model: "gpt-4"
-  model_prov: "openai"
-  format:
-    type: text
-user:
-  language: English
-  role: "A customer looking for general information about the bike shop and its services."
-  context:
-    - "The user is interested in basic services and pricing."
-  goals:
-    - "What are the opening and closing times of the bike shop?"
-    - "How much does a new bike tire cost?"
-    - "What is the price of a standard bike tune-up?"
-    - "How much for a new bike seat?"
-    - "Can you give me general advice on how to take care of a bike?"
-chatbot:
-  is_starter: true
-  fallback: "I'm sorry, I didn't understand that. Can you please rephrase?"
-  output:
-    - opening_hours:
-        type: string
-        description: "The opening and closing times of the bike shop."
-    - tire_price:
-        type: currency
-        description: "The price of a new bike tire."
-    - tune_up_price:
-        type: currency
-        description: "The price of a standard bike tune-up."
-    - seat_price:
-        type: currency
-        description: "The price of a new bike seat."
-    - bike_care_advice:
-        type: string
-        description: "General advice on bike maintenance."
-conversation:
-  number: 1
-  goal_style:
-    steps: 5
-  interaction_style:
-    - single questions
-```
-### Summary of the Profile
-- **Test Name**: "Bike Shop Virtual Assistant Test"
-- **User Role**: Simulates a customer asking about shop hours, pricing, and bike care.
-- **Chatbot Output**: Extracts relevant information such as prices and advice.
-- **Conversation Control**: Designed for a single interaction with a clear structure.
-This profile is set up to test the chatbot's ability to provide accurate and relevant information while adhering to the specified constraints. If you need any adjustments or additional features, just let me know! 😊</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Sure thing! Here’s a profile that captures your requirements for testing a bike shop’s virtual assistant. It focuses on a customer seeking general information about the shop and its standard services, phrasing questions clearly and directly. Let’s dive in! 🚴‍♂️
-```yaml
-test_name: "bike_shop_general_information"
-llm:
-  temperature: 0.5
-  model: gpt-4o-mini
-  format:
-    type: text
-user:
-  language: English
-  role: "A customer looking for general information about the bike shop and its standard services."
-  context:
-    - "You are interested in understanding the basic services offered by the bike shop."
-    - "You want to gather information about pricing and operating hours."
-    - "You are not looking for appointments, specific bike models, or advanced repairs."
-  goals:
-    - "What are the opening and closing times of the bike shop?"
-    - "How much does a new bike tire cost?"
-    - "What is the price of a standard bike tune-up?"
-    - "How much is a new bike seat?"
-    - "Can you give me some general advice on how to take care of my bike?"
-chatbot:
-  is_starter: true
-  fallback: "I'm sorry, it's a little loud in my shop, can you say that again?"
-  output:
-    - opening_and_closing: 
-        type: string
-        description: "The opening and closing times of the bike shop."
-    - tire_price: 
-        type: money
-        description: "The price of a new bike tire."
-    - tune_up_price: 
-        type: money
-        description: "The price of a standard bike tune-up."
-    - seat_price: 
-        type: money
-        description: "The price of a new bike seat."
-    - bike_care_advice: 
-        type: string
-        description: "General advice on how to properly take care of a bike."
-conversation:
-  number: 5
-  goal_style:
-    all_answered:
-      export: true
-      limit: 5
-  interaction_style:
-    - default
-```
-### Breakdown of the Profile:
-- **Test Name**: Clearly identifies the purpose of the profile.
-- **User Role**: Describes the simulated user as a customer seeking basic information.
-- **Context**: Sets the scene for the user’s intentions and limitations on topics.
-- **Goals**: Lists specific questions the user will ask, ensuring clarity and directness.
-- **Chatbot Output**: Defines the expected responses from the chatbot, ensuring it covers all necessary information.
-- **Conversation Controls**: Limits the number of interactions to keep it focused and relevant.
-Feel free to adjust any part of this profile as needed! Happy testing! 😊</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>That sounds like a great profile to create! Below is a YAML profile that captures all your requirements for testing the bike shop’s virtual assistant. It defines the user’s context, goals, and the expected output from the chatbot.
-```yaml
-test_name: "bike_shop_virtual_assistant"
-llm:
-  temperature: 0.6
-  model: gpt-4o-mini
-  format:
-    type: text
-user:
-  language: English
-  role: "A customer seeking general information about the bike shop and its services."
-  context:
-    - "You are looking for basic information about the bike shop's services."
-    - "You want to know about pricing and shop hours."
-    - "You are not interested in advanced repairs, specific bike models, or appointments."
-  goals:
-    - "What are the opening and closing times of the bike shop?"
-    - "How much does a new bike tire cost?"
-    - "What is the price of a standard bike tune-up?"
-    - "How much is a new bike seat?"
-    - "Can you give me some general advice on how to properly take care of my bike?"
-chatbot:
-  is_starter: false
-  fallback: "I'm sorry, it's a little loud in my shop, can you say that again?"
-  output:
-    - opening_and_closing_time:
-        type: string
-        description: "The opening and closing times of the bike shop."
-    - tire_price:
-        type: money
-        description: "The price of a new bike tire."
-    - tune_up_price:
-        type: money
-        description: "The price of a standard bike tune-up."
-    - seat_price:
-        type: money
-        description: "The price of a new bike seat."
-    - maintenance_advice:
-        type: string
-        description: "General advice on how to properly take care of a bike."
-conversation:
-  number: 5
-  goal_style:
-    all_answered:
-      export: true
-      limit: 5
-  interaction_style:
-    - single question
-```
-This profile sets up a clear and direct interaction for the user, focusing on the essential information while ensuring the chatbot stays on topic. Feel free to tweak any details to better fit your specific testing needs! Happy testing! 🚴‍♂️😊</t>
-        </is>
-      </c>
-      <c r="G9" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>20260324_144250_084</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>p33</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>I have this profile, but I don't know what to add to the chatbot field. Can you help me completing it for me?: test_name: pizza_and_drinks_information_seeker
 llm:
@@ -1763,7 +1366,7 @@
   - single question</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Let's enhance the `chatbot` field of your profile to ensure it meets the requirements. Here’s a refined version that includes a valid list for the `chatbot.output` section and addresses the interaction style:
 ```yaml
@@ -1828,7 +1431,7 @@
 This structure should work well for your needs. If you have any further questions or need additional adjustments, feel free to ask! 😊</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>I apologize for not being able to successfully validate your request after three attempts. It seems that you were looking to fix your profile, but there were issues with the required fields. I encourage you to adjust your instructions based on the feedback provided, particularly ensuring that the language field is included. If you need further assistance, please feel free to reach out again. Thank you for your understanding!
 Validator feedback:
@@ -1841,7 +1444,7 @@
 Keep blocks none unchanged. Rewrite the full reply, but only modify blocks 1 and any prose that references them.</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Sure! Let's complete the `chatbot` field for your profile. This section typically includes the `is_starter`, `fallback`, and `output` fields. Here’s a suggestion based on the context of your profile:
 ```yaml
@@ -1868,33 +1471,33 @@
 This setup will help your chatbot provide relevant information based on the user's inquiries. Feel free to adjust the descriptions or types as needed! 😊</t>
         </is>
       </c>
-      <c r="G10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H10" t="b">
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" t="b">
         <v>1</v>
       </c>
-      <c r="I10" t="b">
+      <c r="I8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>20260324_144250_084</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>p50</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>What is an oracle?</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>In the context of SENSEI rules, an "oracle" refers to a validation condition that evaluates to a boolean value (true or false). It is used to determine whether a specific condition in a conversation meets the criteria set by the rule. 
 Here’s a simple breakdown:
@@ -1905,12 +1508,12 @@
 If you need more detailed information or examples, feel free to ask! 😊</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>I can only help with SENSEI rules, SENSEI profiles, SENSEI connectors, or related explanations. Please share one of those requests.</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>In the context of Sensei and testing, an **oracle** is a mechanism used to determine whether the output of a system (like a chatbot) is correct or not. It acts as a reference point to validate the results produced during testing.
 In Sensei-check, oracles can be defined in rules to specify the expected behavior or output for a given input. For example, if you're testing a pizza ordering chatbot, an oracle might check that the total price returned is greater than zero when a valid order is placed.
@@ -1918,28 +1521,28 @@
 If you have any specific questions about how to implement or use oracles in your Sensei project, feel free to ask!</t>
         </is>
       </c>
-      <c r="G11" t="b">
-        <v>0</v>
-      </c>
-      <c r="H11" t="b">
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" t="b">
         <v>1</v>
       </c>
-      <c r="I11" t="b">
+      <c r="I9" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>20260324_153209_153</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>p3</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Hola, tengo este perfil y necesito que me ayudes a arreglarlo por favor
 test_name: Asistencia Técnica y Cuentas
@@ -2015,12 +1618,12 @@
     steps: 30</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Lo siento, he intentado varias veces, pero no pude terminar una versión que cumpla con todos los requisitos. El problema principal es que hay algunos elementos en tus objetivos que no están correctamente declarados. Si puedes proporcionar más detalles sobre esos elementos, estaré encantado de ayudarte a solucionarlo. 😊</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>¡Hola! 😊 Estoy aquí para ayudarte a arreglar tu perfil. He notado algunos detalles que necesitan ajustes. Aquí tienes una versión corregida y mejor estructurada:
 ```yaml
@@ -2107,7 +1710,7 @@
 ¡Espero que esto te ayude! Si necesitas más ajustes o tienes alguna otra pregunta, ¡no dudes en decírmelo! 😊</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>¡Hola! 😊 Vamos a revisar y arreglar tu perfil. He notado algunos problemas de formato y estructura que podrían causar errores. Aquí tienes una versión corregida:
 ```yaml
@@ -2191,28 +1794,28 @@
 ¡Espero que esto te ayude! Si necesitas más ajustes o tienes alguna otra pregunta, aquí estoy para ayudarte. 😊</t>
         </is>
       </c>
-      <c r="G12" t="b">
+      <c r="G10" t="b">
         <v>1</v>
       </c>
-      <c r="H12" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" t="b">
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>20260324_153209_153</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>I have this profile that has a lot of things but I dont know how to try it, could you suggest me a rule or more to do it?
 test_name: Usuarios Nuevos y Admisiones
@@ -2315,12 +1918,12 @@
   - single questions</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>I'm sorry, but I tried several times and couldn't finish a version that meets all the requirements. The main issue is with some rules not being formatted correctly. If you have any specific examples or details you'd like to share, that could help us get it right!</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>¡Hola! 😊 It sounds like you have a fantastic profile set up for potential students looking for admission information! Let's create some rules to help you test it effectively.
 Here are a couple of rule suggestions that you can use with your profile:
@@ -2377,7 +1980,7 @@
 Feel free to adjust the names, descriptions, or conditions to better fit your needs! These rules will help you ensure that your chatbot is providing the necessary information to potential students. If you have any more specific scenarios in mind or need further assistance, just let me know! 😊</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>That sounds like a great profile! To help you test it effectively, I suggest creating a few Sensei rules that focus on the outputs your profile generates. Here are some rules you might consider:
 ### 1. Check for Required Outputs
@@ -2424,38 +2027,38 @@
 Feel free to adjust the descriptions and conditions based on your specific needs! Just copy these YAML blocks into your rules directory, and you'll be ready to test your profile. Happy testing! 😊</t>
         </is>
       </c>
-      <c r="G13" t="b">
+      <c r="G11" t="b">
         <v>1</v>
       </c>
-      <c r="H13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13" t="b">
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>20260324_153209_153</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>p19</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Create a rule to check if the chatbot provided information about current promotions. this rule is not based on any profile, use the variables you want</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>I'm sorry, but I tried several times to create the rule, and I couldn't get it right. The main issue is with the structure of the rule itself. If you have any specific details or examples you'd like to share, that could help!</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Sure! Since you're looking for a rule that checks if the chatbot provided information about current promotions without being tied to a specific profile, we can create a global rule. This rule will focus on ensuring that the chatbot mentions promotions in the conversation.
 Here's a sample YAML rule you can use:
@@ -2474,7 +2077,7 @@
 Feel free to adjust the keyword "promotions" to match any specific terms you expect the chatbot to use! If you have any other requests or need further adjustments, just let me know! 😊</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Sure! Here's a global rule that checks if the chatbot provided information about current promotions. Since it's not based on any specific profile, it uses a general approach.
 ```yaml
@@ -2486,33 +2089,33 @@
 This rule will verify that the `data_output` contains the field `current_promotions`, indicating that the chatbot has shared information about promotions. If you have any adjustments or specific requirements in mind, feel free to let me know! 😊</t>
         </is>
       </c>
-      <c r="G14" t="b">
+      <c r="G12" t="b">
         <v>1</v>
       </c>
-      <c r="H14" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" t="b">
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>20260324_153209_153</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>p24</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Create a profile to test a bike shop’s virtual assistant. The user should be a customer interacting in English who is looking for general information about the shop and its standard services. During the interaction, the user should ask about the opening and closing times of the bike shop, the price of a new bike tire, the price of a standard bike tune-up, and the price of a new bike seat. In addition, the user should ask for general advice on how to properly take care of a bike, focusing on basic maintenance and good practices rather than advanced repairs. The user must behave like a normal customer and phrase questions clearly and directly. The user should not ask about appointments, specific bike models, custom or advanced repairs, warranties, delivery services, or any topic outside of basic pricing, shop hours, and general bike care. This profile is intended to test whether the chatbot provides accurate and relevant information for each request, uses appropriate bike-shop terminology, clearly states prices, and avoids introducing unrelated services or unsolicited suggestions.</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>I've loaded the relevant documentation for profiles from `sensei-chat-guide.md`. Now, let's create a profile for the bike shop's virtual assistant based on your specifications. Here's the proposed YAML structure:
 ```yaml
@@ -2570,7 +2173,7 @@
 Would you like to make any adjustments to this profile, or should I proceed to save it? 😊</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Sure! Here’s a profile tailored to test a bike shop’s virtual assistant based on your requirements. This profile ensures that the user behaves like a typical customer, asking clear and direct questions about the shop's services and pricing. 
 ```yaml
@@ -2630,7 +2233,7 @@
 Feel free to adjust any parts of the profile to better fit your needs! Happy testing! 😊</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>That sounds like a great profile to create! Here's a YAML profile that captures all your requirements for testing the bike shop's virtual assistant. It includes the user's goals, context, and interaction style to ensure a smooth and focused conversation. 😊
 ```yaml
@@ -2683,28 +2286,28 @@
 This profile is structured to ensure that the user interacts clearly and directly, focusing on the essential information about the bike shop. It also specifies the expected outputs from the chatbot, making it easier to validate the responses. Happy testing! 🚴‍♂️</t>
         </is>
       </c>
-      <c r="G15" t="b">
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" t="b">
         <v>1</v>
       </c>
-      <c r="H15" t="b">
-        <v>0</v>
-      </c>
-      <c r="I15" t="b">
-        <v>1</v>
-      </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>20260324_153209_153</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>p31</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Fix this profile: test_name: general_information_seeker
 llm:
@@ -2752,12 +2355,12 @@
   - single question</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>I'm sorry, but I tried several times and couldn't finish a version that meets all requirements. The main issue is with the interaction style; it needs to be one of the allowed options. If you have any specific preferences, please let me know!</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Sure! Let's tidy up your profile for `general_information_seeker`. It looks like there are a few formatting issues and some inconsistencies in the data types. Here's a corrected version:
 ```yaml
@@ -2815,7 +2418,7 @@
 Feel free to let me know if you need any more help! 😊</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>It looks like there are a few formatting issues in your profile that need to be addressed, particularly with indentation and the structure of the YAML. Let’s fix that up! Here’s the corrected version of your profile:
 ```yaml
@@ -2872,28 +2475,28 @@
 Feel free to let me know if you need any more adjustments or have further questions! 😊</t>
         </is>
       </c>
-      <c r="G16" t="b">
+      <c r="G14" t="b">
         <v>1</v>
       </c>
-      <c r="H16" t="b">
-        <v>0</v>
-      </c>
-      <c r="I16" t="b">
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>20260324_153209_153</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>p33</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>I have this profile, but I don't know what to add to the chatbot field. Can you help me completing it for me?: test_name: pizza_and_drinks_information_seeker
 llm:
@@ -2927,12 +2530,12 @@
   - single question</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>I'm sorry, but I tried several times and couldn't finish the chatbot section for you. It looks like we need to include some top-level fields like `conversation`, `test_name`, and `user`. If you have any specific details or examples for those, please share!</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Absolutely, I’d be happy to help you complete the `chatbot` field for your profile! 😊
 In the `chatbot` section, you'll want to define how the chatbot should respond to the user's inquiries. This includes setting a fallback message for when the chatbot doesn't understand a question and specifying the outputs you want to extract after the conversation. Here's a suggestion for your `chatbot` field:
@@ -2975,7 +2578,7 @@
 Feel free to adjust any of the descriptions or types based on your specific needs! Happy testing! 🍕✨</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Sure! It looks like you're off to a great start with your profile. For the `chatbot` field, you'll want to define the outputs that you expect from the chatbot after the conversation. Here’s a suggestion for what you could include in the `chatbot` field:
 ```yaml
@@ -3011,38 +2614,38 @@
 Feel free to adjust the descriptions or types based on your specific needs! 😊</t>
         </is>
       </c>
-      <c r="G17" t="b">
+      <c r="G15" t="b">
         <v>1</v>
       </c>
-      <c r="H17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I17" t="b">
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>20260324_153209_153</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>p37</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Cera una regla que compruebe en la conversación si el asistente confirma que añadió la bebida que el usuario pidió.</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Lo siento, he intentado varias veces, pero no pude completar la regla que necesitas. El problema principal es que hay un error en la estructura que impide que sea válida. Si tienes ejemplos o detalles adicionales sobre cómo debería lucir, estaré encantado de ayudar. 😊</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>¡Hola! 😊 Para crear una regla que verifique si el asistente confirma que añadió la bebida que el usuario pidió, podemos usar la estructura de las reglas de Sensei-check. Aquí tienes un ejemplo de cómo podría verse esta regla:
 ```yaml
@@ -3059,7 +2662,7 @@
 Recuerda ajustar las frases específicas en el `oracle` según cómo se formulen en tu proyecto. Si necesitas más ayuda o ajustes, ¡no dudes en decírmelo! 😊</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>¡Claro! Para crear una regla que verifique si el asistente confirma que ha añadido la bebida que el usuario pidió, podemos usar una regla de tipo metamórfica. Aquí tienes un ejemplo de cómo podría verse esa regla:
 ```yaml
@@ -3078,28 +2681,28 @@
 Asegúrate de ajustar el texto en las condiciones `if` y `then` según las frases exactas que utiliza tu asistente y usuario en las conversaciones. ¡Espero que esto te ayude! Si necesitas más ajustes, no dudes en decírmelo 😊.</t>
         </is>
       </c>
-      <c r="G18" t="b">
+      <c r="G16" t="b">
         <v>1</v>
       </c>
-      <c r="H18" t="b">
-        <v>0</v>
-      </c>
-      <c r="I18" t="b">
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>20260324_153209_153</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>p46</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>I have this connector but it is not working. Fix it using the request and response below. The fixed connector must use base_url, path, headers, payload_template, and the correct response_path to extract the assistant message, not the user request. Keep Authorization exactly as provided (do not change it to Bearer). Return the corrected YAML only.
 Broken connector:
@@ -3127,12 +2730,12 @@
 {""request"":{""text"":""hola""},""response"":[{""showUserFeedback"":false,""platform"":""PLATFORM_UNSPECIFIED"",""text"":""&lt;p&gt;¡Buenos días!&lt;br&gt;&lt;br&gt;¿En qué puedo ayudarte?&lt;/p&gt;"",""message"":""text""}]}</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>I'm sorry, but I tried several times and couldn't get your connector to pass all checks. The main issue is with the `response_path`, which needs to be corrected. If you have any specific details or examples, please share them!</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Here's the corrected YAML for your connector:
 ```yaml
@@ -3158,7 +2761,7 @@
 This should help you extract the assistant's message correctly! If you need any more assistance, just let me know! 😊</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Here's the corrected YAML for your connector:
 ```yaml
@@ -3183,33 +2786,33 @@
 ```</t>
         </is>
       </c>
-      <c r="G19" t="b">
+      <c r="G17" t="b">
         <v>1</v>
       </c>
-      <c r="H19" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" t="b">
+      <c r="H17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>20260324_153209_153</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>p50</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>What is an oracle?</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>In the context of SENSEI rules, an **oracle** is a validation condition used to determine whether a specific condition is true or false during a conversation. It acts as a check that can help validate the outputs or behaviors of a chatbot against expected criteria.
 ### Key Points about Oracles:
@@ -3220,12 +2823,12 @@
 If you have more specific questions about how oracles are used in SENSEI rules or need help with a particular rule, feel free to ask! 😊</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>I can only help with SENSEI rules, SENSEI profiles, SENSEI connectors, or related explanations. Please share one of those requests.</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>In the context of Sensei and chatbot testing, an **oracle** is a mechanism or rule used to determine whether the output of a chatbot is correct or not. It acts as a reference point to validate the responses generated by the chatbot during testing.
 For example, an oracle might specify that the chatbot should return a certain value when given a specific input. If the chatbot's output matches the expected value defined by the oracle, then the test is considered successful. If it doesn't match, the test fails.
@@ -3233,28 +2836,28 @@
 If you have more specific questions about how to implement oracles in your Sensei project, feel free to ask!</t>
         </is>
       </c>
-      <c r="G20" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20" t="b">
+      <c r="G18" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" t="b">
         <v>1</v>
       </c>
-      <c r="I20" t="b">
+      <c r="I18" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>20260324_163215_740</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>p3</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Hola, tengo este perfil y necesito que me ayudes a arreglarlo por favor
 test_name: Asistencia Técnica y Cuentas
@@ -3330,12 +2933,12 @@
     steps: 30</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Lo siento, he intentado varias veces, pero no pude completar una versión que cumpla con todos los requisitos. El problema principal es que hay algunos elementos en la lista de objetivos que necesitan ser declarados primero. Si tienes más detalles o ejemplos, estaré encantado de ayudarte. 😊</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>¡Hola! 😊 Vamos a revisar y arreglar tu perfil de "Asistencia Técnica y Cuentas". He notado algunos detalles que necesitan ajustes para que todo funcione correctamente. Aquí tienes una versión corregida:
 ```yaml
@@ -3422,7 +3025,7 @@
 ¡Espero que esto te ayude! Si necesitas más ajustes o tienes alguna otra pregunta, ¡no dudes en decírmelo! 😊</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>¡Hola! 😊 Estoy aquí para ayudarte a arreglar tu perfil. He notado algunos problemas de formato y estructura en tu YAML. Vamos a corregirlo para que funcione correctamente. Aquí tienes la versión ajustada:
 ```yaml
@@ -3506,28 +3109,28 @@
 ¡Espero que esto te ayude! Si necesitas más ajustes o tienes alguna otra pregunta, no dudes en decírmelo. 😊</t>
         </is>
       </c>
-      <c r="G21" t="b">
+      <c r="G19" t="b">
         <v>1</v>
       </c>
-      <c r="H21" t="b">
-        <v>0</v>
-      </c>
-      <c r="I21" t="b">
+      <c r="H19" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>20260324_163215_740</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>I have this profile that has a lot of things but I dont know how to try it, could you suggest me a rule or more to do it?
 test_name: Usuarios Nuevos y Admisiones
@@ -3630,12 +3233,12 @@
   - single questions</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>I'm sorry, but I tried several times and couldn't finish a version that meets all the requirements. The main issue is that some rules need to be adjusted for proper formatting. If you have any specific examples or details you'd like to share, that could help!</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>¡Hola! 😊 It sounds like you have a really interesting profile for potential students looking for admission information! Let's create some Sensei-check rules to test it out. Here are a couple of suggestions that could help you ensure the chatbot provides accurate and relevant information:
 ### 1. Admission Link Availability
@@ -3689,7 +3292,7 @@
 Feel free to adapt these rules to better fit your specific needs or to add more rules based on other outputs in your profile! Testing these rules will help ensure that your chatbot is providing the necessary information to potential students. If you have any questions or need further assistance, just let me know! 😊</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>That sounds like a great profile! To effectively test it, you can create some rules that validate the outputs based on the goals you've defined. Here are a few suggestions for rules that you might find useful:
 ### 1. Rule to Check for Admission Information Availability
@@ -3735,225 +3338,28 @@
 Feel free to adjust the descriptions or add more rules based on specific aspects of your profile that you want to test. Each of these rules will help you verify that your chatbot is functioning as expected and providing the necessary information to potential students. Happy testing! 😊</t>
         </is>
       </c>
-      <c r="G22" t="b">
+      <c r="G20" t="b">
         <v>1</v>
       </c>
-      <c r="H22" t="b">
-        <v>0</v>
-      </c>
-      <c r="I22" t="b">
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>20260324_163215_740</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>p24</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Create a profile to test a bike shop’s virtual assistant. The user should be a customer interacting in English who is looking for general information about the shop and its standard services. During the interaction, the user should ask about the opening and closing times of the bike shop, the price of a new bike tire, the price of a standard bike tune-up, and the price of a new bike seat. In addition, the user should ask for general advice on how to properly take care of a bike, focusing on basic maintenance and good practices rather than advanced repairs. The user must behave like a normal customer and phrase questions clearly and directly. The user should not ask about appointments, specific bike models, custom or advanced repairs, warranties, delivery services, or any topic outside of basic pricing, shop hours, and general bike care. This profile is intended to test whether the chatbot provides accurate and relevant information for each request, uses appropriate bike-shop terminology, clearly states prices, and avoids introducing unrelated services or unsolicited suggestions.</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>I've loaded the relevant documentation for profiles from `sensei-chat-guide.md`. Now, let's create a profile for the bike shop's virtual assistant based on your requirements.
-### Profile Structure
-Here's the proposed structure for the profile:
-```yaml
-test_name: "bike_shop_virtual_assistant"
-llm:
-  temperature: 0.7
-  model: gpt-4o
-  model_prov: openai
-  format:
-    type: text
-user:
-  language: English
-  role: "A customer interacting with a bike shop's virtual assistant to inquire about general information."
-  context:
-    - "The user is looking for information about shop hours, pricing for services, and basic bike maintenance."
-  goals:
-    - "What are the opening and closing times of the bike shop?"
-    - "How much does a new bike tire cost?"
-    - "What is the price of a standard bike tune-up?"
-    - "How much is a new bike seat?"
-    - "Can you give me some general advice on how to take care of a bike?"
-chatbot:
-  is_starter: true
-  fallback: "I'm sorry, I can't help with that."
-  output:
-    - opening_hours:
-        type: string
-        description: "The opening and closing times of the bike shop."
-    - tire_price:
-        type: currency
-        description: "The price of a new bike tire."
-    - tune_up_price:
-        type: currency
-        description: "The price of a standard bike tune-up."
-    - seat_price:
-        type: currency
-        description: "The price of a new bike seat."
-    - maintenance_advice:
-        type: string
-        description: "General advice on bike maintenance."
-conversation:
-  number: 5
-  goal_style:
-    steps: 5
-  interaction_style:
-    - single questions
-```
-### Summary of the Profile
-- **Test Name**: This profile is named "bike_shop_virtual_assistant" to clearly indicate its purpose.
-- **User Role**: The user is defined as a customer seeking general information about the bike shop.
-- **Goals**: The profile outlines specific questions the user will ask, focusing on shop hours, pricing, and basic maintenance advice.
-- **Chatbot Output**: The profile specifies what information should be extracted after the conversation, including prices and maintenance advice.
-- **Conversation Control**: The profile is set to allow for five interactions, ensuring a thorough testing of the assistant's responses.
-Would you like to proceed with creating this profile, or do you have any modifications in mind? 😊</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Sure thing! Here’s a profile tailored for testing a bike shop's virtual assistant, focusing on general information and standard services. This profile ensures the user behaves like a typical customer, asking clear and direct questions. Let’s dive in! 🚴‍♂️
-```yaml
-test_name: "bike_shop_general_information"
-llm:
-  temperature: 0.5
-  model: gpt-4o-mini
-  format:
-    type: text
-user:
-  language: English
-  role: "A customer looking for general information about the bike shop and its standard services."
-  context:
-    - "You are interested in understanding the basic services offered by the bike shop."
-    - "You want to gather information about pricing and shop hours."
-  goals:
-    - "What are the opening and closing times of the bike shop?"
-    - "How much does a new bike tire cost?"
-    - "What is the price of a standard bike tune-up?"
-    - "How much is a new bike seat?"
-    - "Can you give me some general advice on how to properly take care of my bike?"
-chatbot:
-  is_starter: true
-  fallback: "I'm sorry, could you please repeat that?"
-  output:
-    - opening_and_closing: 
-        type: string
-        description: "The opening and closing times of the bike shop."
-    - tire_price: 
-        type: money
-        description: "The price of a new bike tire."
-    - tune_up_price: 
-        type: money
-        description: "The price of a standard bike tune-up."
-    - seat_price: 
-        type: money
-        description: "The price of a new bike seat."
-    - maintenance_advice: 
-        type: string
-        description: "General advice on how to properly take care of a bike."
-conversation:
-  number: 5
-  goal_style:
-    all_answered:
-      export: true
-      limit: 5
-  interaction_style:
-    - default
-```
-### Explanation:
-- **Test Name**: Clearly defines the purpose of the profile.
-- **User Role**: Describes the user as a customer seeking basic information.
-- **Goals**: Lists specific questions the user will ask, ensuring they stay within the defined scope.
-- **Chatbot Output**: Specifies what information the chatbot should provide, focusing on relevant topics.
-- **Conversation Controls**: Sets the number of interactions and ensures all goals are addressed.
-Feel free to tweak any part of this profile to better fit your testing needs! Happy testing! 😊</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Sure! Here’s a profile designed for testing a bike shop’s virtual assistant, focusing on the specified user behavior and inquiries. This profile ensures that the user interacts clearly and directly while sticking to the relevant topics. 
-```yaml
-test_name: "Bike Shop Virtual Assistant Inquiry"
-llm:
-  temperature: 0.7
-  model: gpt-4o
-  format:
-    type: text
-user:
-  language: English
-  role: "A customer seeking general information about the bike shop and its services."
-  context:
-    - "You are looking for basic information about the bike shop's services and pricing."
-    - "You want to ensure you understand the shop's offerings without delving into advanced repairs or unrelated topics."
-  goals:
-    - "What are the opening and closing times of the bike shop?"
-    - "How much does a new bike tire cost?"
-    - "What is the price for a standard bike tune-up?"
-    - "How much is a new bike seat?"
-    - "Can you give me some general advice on how to properly take care of my bike?"
-chatbot:
-  is_starter: false
-  fallback: "I'm sorry, I didn't quite catch that. Could you please repeat your question?"
-  output:
-    - opening_and_closing: 
-        type: string
-        description: "The opening and closing times of the bike shop."
-    - tire_price: 
-        type: money
-        description: "The price of a new bike tire."
-    - tune_up_price: 
-        type: money
-        description: "The price for a standard bike tune-up."
-    - seat_price: 
-        type: money
-        description: "The price of a new bike seat."
-    - maintenance_advice: 
-        type: string
-        description: "General advice on how to properly take care of a bike."
-conversation:
-  number: 5
-  goal_style:
-    all_answered:
-      export: true
-      limit: 5
-  interaction_style:
-    - default
-```
-This profile sets the stage for a clear and focused interaction with the virtual assistant, ensuring that the user sticks to the relevant topics and receives accurate information. Let me know if you need any adjustments or additional details! 😊</t>
-        </is>
-      </c>
-      <c r="G23" t="b">
-        <v>1</v>
-      </c>
-      <c r="H23" t="b">
-        <v>0</v>
-      </c>
-      <c r="I23" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>20260324_163215_740</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>p31</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Fix this profile: test_name: general_information_seeker
 llm:
@@ -4001,12 +3407,12 @@
   - single question</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>I'm sorry, but I tried several times and couldn't finish a version that meets all requirements. The main issue is that the interaction style needs to be one of the allowed options. If you have any specific preferences or examples, please share!</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Sure! It looks like your profile has a few formatting issues and a minor inconsistency in the data types. Let's fix that up for you! Here’s the corrected version of the `general_information_seeker` profile:
 ```yaml
@@ -4064,7 +3470,7 @@
 Feel free to let me know if you need any more help! Happy testing! 😊</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>It looks like your profile has a few formatting issues that need to be fixed for it to work properly. Here’s a corrected version of your `general_information_seeker` profile:
 ```yaml
@@ -4121,28 +3527,28 @@
 Feel free to copy and paste this corrected version into your profile file! If you need any more help, just let me know! 😊</t>
         </is>
       </c>
-      <c r="G24" t="b">
+      <c r="G21" t="b">
         <v>1</v>
       </c>
-      <c r="H24" t="b">
-        <v>0</v>
-      </c>
-      <c r="I24" t="b">
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>20260324_163215_740</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>p33</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>I have this profile, but I don't know what to add to the chatbot field. Can you help me completing it for me?: test_name: pizza_and_drinks_information_seeker
 llm:
@@ -4176,12 +3582,12 @@
   - single question</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>I'm sorry, but I tried several times and couldn't finish a version that meets all requirements. It looks like we need to include some top-level fields like conversation, test_name, and user. If you have any specific details or examples to share, that would help!</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>I sincerely apologize for the repeated validation failures you've experienced. We attempted to validate your request three times, but it seems there were issues with the profile you wanted to fix. Specifically, the 'user.language' field was missing. I encourage you to adjust your instructions based on the feedback provided or try adding the necessary information to ensure a successful validation. If you need further assistance, feel free to reach out again. Thank you for your understanding!
 Validator feedback:
@@ -4194,7 +3600,7 @@
 Keep blocks none unchanged. Rewrite the full reply, but only modify blocks 1 and any prose that references them.</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Absolutely, I'd be happy to help you complete the `chatbot` field for your profile! Here’s a suggested structure based on the context and goals you've provided. This includes the `fallback` message and the `output` fields that you might want to extract after the conversation:
 ```yaml
@@ -4221,33 +3627,33 @@
 This structure provides a clear outline of what the chatbot should respond with and what information you want to extract from the conversation. Feel free to adjust the descriptions or types as needed! 😊</t>
         </is>
       </c>
-      <c r="G25" t="b">
+      <c r="G22" t="b">
         <v>1</v>
       </c>
-      <c r="H25" t="b">
+      <c r="H22" t="b">
         <v>1</v>
       </c>
-      <c r="I25" t="b">
+      <c r="I22" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>20260324_163215_740</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>p50</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>What is an oracle?</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>In the context of SENSEI rules, an **oracle** is a validation condition used to determine whether a specific condition is true or false during the evaluation of a chatbot conversation. It serves as a way to check if the chatbot's responses or behaviors meet certain criteria defined in the rules.
 ### Key Points about Oracles:
@@ -4257,422 +3663,40 @@
 If you need more specific examples or details about how oracles are structured in SENSEI rules, let me know! 😊</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>I can only help with SENSEI rules, SENSEI profiles, SENSEI connectors, or related explanations. Please share one of those requests.</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>In the context of Sensei and testing, an **oracle** is a mechanism or method used to determine whether the output of a system (like a chatbot) is correct or not. It acts as a reference point against which the actual output can be compared.
 For example, in Sensei-check, an oracle can be a simple condition that checks if certain expected values are present in the chatbot's response. If the actual output meets the conditions defined by the oracle, it is considered correct; if not, it indicates a failure.
 In summary, oracles help validate the correctness of the system's behavior by providing expected outcomes to compare against! 😊 If you have more questions about how oracles work in Sensei or anything else, feel free to ask!</t>
         </is>
       </c>
-      <c r="G26" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" t="b">
+      <c r="G23" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" t="b">
         <v>1</v>
       </c>
-      <c r="I26" t="b">
+      <c r="I23" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>20260324_172746_454</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>p22</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>We need a profile for a user that is at discomfort when riding his bike and he is not sure if it is the bike is not fit correctly or that his components are worn. The user wants advice on possible adjustments or services the shop offers, but does not explicitly ask to book an appointment.</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Great! I've loaded the relevant documentation for profiles from `sensei-chat-guide.md`. Now, let's create a profile for the user who is experiencing discomfort while riding their bike and is seeking advice on adjustments or services.
-### Profile Structure
-Based on the documentation, here's how we can structure the profile:
-1. **Test Name**: A descriptive name for the profile.
-2. **LLM Settings**: Configuration for the language model.
-3. **User Context**: Information about the user, including their discomfort and the context of their inquiry.
-4. **Goals**: Specific goals that the user wants to achieve, such as asking for advice on bike adjustments or services.
-5. **Chatbot Output**: Fields that we want to extract from the conversation for validation.
-### Proposed Profile YAML
-Here's a proposed YAML structure for the profile:
-```yaml
-test_name: "Bike Discomfort Inquiry"
-llm:
-  temperature: 0.7
-  model: gpt-4o
-  model_prov: openai
-  format:
-    type: text
-user:
-  language: English
-  role: "A cyclist experiencing discomfort while riding their bike."
-  context:
-    - "The user is unsure if the discomfort is due to bike fit or worn components."
-  goals:
-    - "Ask for advice on possible adjustments to the bike."
-    - "Inquire about services offered by the shop for bike maintenance."
-chatbot:
-  is_starter: true
-  fallback: "I'm sorry, could you clarify that?"
-  output:
-    - advice:
-        type: string
-        description: "Advice on bike adjustments or services available."
-conversation:
-  number: 3
-  goal_style:
-    steps: 5
-  interaction_style:
-    - random:
-      - long phrases
-      - single questions
-```
-### Explanation of the Profile
-- **Test Name**: Clearly indicates the purpose of the profile.
-- **LLM Settings**: Configured for a conversational style.
-- **User Role and Context**: Provides necessary background about the user’s situation.
-- **Goals**: Specifies what the user wants to achieve in the conversation.
-- **Chatbot Output**: Defines what information we want to extract from the conversation.
-- **Conversation Controls**: Sets the number of interactions and styles for how the user will communicate.
-Would you like to make any adjustments to this profile, or should I proceed to save it as a YAML file? 😊</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Creating a profile for a user who is experiencing discomfort while riding their bike sounds like a great way to simulate a realistic scenario! Here’s a draft profile that captures the essence of your request:
-```yaml
-test_name: "bike_discomfort_advice_seeker"
-llm:
-  temperature: 0.6
-  model: gpt-4o-mini
-  format:
-    type: text
-user:
-  language: English
-  role: "A cyclist experiencing discomfort while riding and seeking advice."
-  context:
-    - "You are unsure if the discomfort is due to improper bike fit or worn components."
-    - "You want to explore possible adjustments or services that can help alleviate the discomfort."
-  goals:
-    - "Inquire about adjustments that can be made to improve bike fit."
-    - "Ask about common signs of worn components and how to identify them."
-    - "Request information on services offered by the shop that could help with bike discomfort."
-    - "Seek advice on how to ensure your bike is properly fitted for comfort."
-chatbot:
-  is_starter: false
-  fallback: "I'm sorry, it's a little loud in my shop, can you say that again?"
-  output:
-    - bike_fit_adjustments:
-        type: string
-        description: "Information on adjustments to improve bike fit."
-    - worn_components_signs:
-        type: string
-        description: "Common signs of worn components and how to identify them."
-    - service_options:
-        type: string
-        description: "Services offered by the shop that could help with bike discomfort."
-    - comfort_improvement_advice:
-        type: string
-        description: "Advice on ensuring proper bike fit for comfort."
-conversation:
-  number: 4
-  goal_style:
-    all_answered:
-      export: false
-      limit: 5
-  interaction_style:
-    - default
-```
-### Explanation of the Profile:
-- **Role**: The user is defined as a cyclist seeking advice, which sets the context for the conversation.
-- **Context**: This section provides background on the user's discomfort and their uncertainty about the cause.
-- **Goals**: The goals focus on inquiries about adjustments, signs of wear, and available services, without explicitly asking to book an appointment.
-- **Chatbot Output**: The output fields are designed to capture the information the user is seeking, which can be validated later.
-Feel free to adjust any part of this profile to better match your needs! If you have any more requests or need further modifications, just let me know! 😊</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>That sounds like a great profile to create! Here’s a YAML profile that captures the essence of a user experiencing discomfort while riding their bike and seeking advice on adjustments or services without explicitly asking for an appointment.
-```yaml
-test_name: "bike_discomfort_advice_seeker"
-llm:
-  temperature: 0.6
-  model: gpt-4o-mini
-  format:
-    type: text
-user:
-  language: English
-  role: "A cyclist experiencing discomfort while riding and seeking advice."
-  context:
-    - "You feel discomfort when riding your bike and are unsure if it's due to improper fit or worn components."
-    - "You want to know what adjustments can be made or what services the shop offers to improve your riding experience."
-  goals:
-    - "Ask for advice on possible adjustments to improve comfort while riding."
-    - "Inquire about services the shop offers for bike fitting or component checks."
-    - "Ask if there are common issues that could cause discomfort while riding."
-    - "Request information on how to identify if components are worn."
-chatbot:
-  is_starter: false
-  fallback: "I'm sorry, it's a little loud in my shop, can you say that again?"
-  output:
-    - adjustment_advice:
-        type: string
-        description: "Advice on bike adjustments to improve comfort."
-    - service_offerings:
-        type: string
-        description: "Information on services offered for bike fitting or component checks."
-    - common_issues:
-        type: string
-        description: "Common issues that could cause discomfort while riding."
-    - component_wear_indicators:
-        type: string
-        description: "How to identify if bike components are worn."
-conversation:
-  number: 5
-  goal_style:
-    all_answered:
-      export: true
-      limit: 5
-  interaction_style:
-    - single question
-```
-Feel free to modify any parts to better fit your needs! This profile should help simulate a user who is looking for guidance while dealing with discomfort on their bike. Happy testing! 🚴‍♂️😊</t>
-        </is>
-      </c>
-      <c r="G27" t="b">
-        <v>1</v>
-      </c>
-      <c r="H27" t="b">
-        <v>0</v>
-      </c>
-      <c r="I27" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>20260324_172746_454</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>p24</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Create a profile to test a bike shop’s virtual assistant. The user should be a customer interacting in English who is looking for general information about the shop and its standard services. During the interaction, the user should ask about the opening and closing times of the bike shop, the price of a new bike tire, the price of a standard bike tune-up, and the price of a new bike seat. In addition, the user should ask for general advice on how to properly take care of a bike, focusing on basic maintenance and good practices rather than advanced repairs. The user must behave like a normal customer and phrase questions clearly and directly. The user should not ask about appointments, specific bike models, custom or advanced repairs, warranties, delivery services, or any topic outside of basic pricing, shop hours, and general bike care. This profile is intended to test whether the chatbot provides accurate and relevant information for each request, uses appropriate bike-shop terminology, clearly states prices, and avoids introducing unrelated services or unsolicited suggestions.</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Great! I've loaded the relevant documentation for profiles from `sensei-chat-guide.md`. Now, let's create a profile for testing the bike shop's virtual assistant. Here's how the profile will be structured:
-### Profile Structure
-- **Test Name**: A descriptive name for the profile.
-- **LLM Settings**: Configuration for the language model.
-- **User Details**: Language, role, context, and goals.
-- **Chatbot Output**: Fields to extract after the conversation.
-- **Conversation Controls**: Number of interactions and styles.
-### Proposed YAML Profile
-```yaml
-test_name: "bike_shop_virtual_assistant"
-llm:
-  temperature: 0.7
-  model: "gpt-4"
-  model_prov: "openai"
-  format:
-    type: text
-user:
-  language: English
-  role: "A customer seeking general information about the bike shop and its services."
-  context:
-    - "The user is interested in shop hours, pricing for bike services, and basic bike maintenance advice."
-  goals:
-    - "What are the opening and closing times of the bike shop?"
-    - "How much does a new bike tire cost?"
-    - "What is the price for a standard bike tune-up?"
-    - "How much for a new bike seat?"
-    - "Can you give me some general advice on how to take care of my bike?"
-chatbot:
-  is_starter: true
-  fallback: "I'm sorry, I can't help with that."
-  output:
-    - opening_hours:
-        type: string
-        description: "The shop's opening and closing times."
-    - tire_price:
-        type: currency
-        description: "Price of a new bike tire."
-    - tune_up_price:
-        type: currency
-        description: "Price for a standard bike tune-up."
-    - seat_price:
-        type: currency
-        description: "Price for a new bike seat."
-    - maintenance_advice:
-        type: string
-        description: "General advice on bike maintenance."
-conversation:
-  number: 5
-  goal_style:
-    steps: 5
-  interaction_style:
-    - single questions
-```
-### Summary of the Profile
-- **Purpose**: This profile simulates a customer asking about the bike shop's services, focusing on shop hours, pricing, and basic maintenance advice.
-- **Output Fields**: The output fields are designed to capture the relevant information provided by the chatbot.
-Would you like me to proceed with creating this profile in the project? 😊</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Sure! Here's a profile you can use to test a bike shop's virtual assistant. This profile captures the essence of a customer seeking general information about the shop and its standard services. Feel free to adjust any details as needed! 😊
-```yaml
-test_name: "bike_shop_general_information"
-llm:
-  temperature: 0.5
-  model: gpt-4o-mini
-  format:
-    type: text
-user:
-  language: English
-  role: "A customer seeking general information about the bike shop and its standard services."
-  context:
-    - "You want to gather basic information about the shop's services and operating hours before visiting."
-    - "You are interested in understanding pricing for common bike-related services."
-  goals:
-    - "What are the opening and closing times of the bike shop?"
-    - "How much does a new bike tire cost?"
-    - "What is the price of a standard bike tune-up?"
-    - "How much is a new bike seat?"
-    - "Can you give me some general advice on how to properly take care of my bike?"
-chatbot:
-  is_starter: true
-  fallback: "I'm sorry, it's a little loud in my shop, can you say that again?"
-  output:
-    - opening_and_closing: 
-        type: string
-        description: "The opening and closing times of the bike shop."
-    - tire_price: 
-        type: money
-        description: "The price of a new bike tire."
-    - tune_up_price: 
-        type: money
-        description: "The price of a standard bike tune-up."
-    - seat_price: 
-        type: money
-        description: "The price of a new bike seat."
-    - maintenance_advice: 
-        type: string
-        description: "General advice on how to properly take care of a bike."
-conversation:
-  number: 5
-  goal_style:
-    all_answered:
-      export: true
-      limit: 5
-  interaction_style:
-    - default
-```
-### Explanation:
-- **Test Name**: Clearly identifies the purpose of the profile.
-- **User Role**: Describes the user's intention and context.
-- **Goals**: Lists the specific questions the user will ask, ensuring they stay within the defined scope.
-- **Chatbot Output**: Specifies what the chatbot should provide in response to each question.
-- **Conversation Control**: Sets the number of interactions and ensures all goals are answered.
-This profile should help you effectively test the chatbot's ability to provide accurate and relevant information while adhering to the specified guidelines. Happy testing! 🚴‍♂️</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Sure thing! Here’s a profile designed for testing a bike shop’s virtual assistant, focusing on the specific user interactions you described. This profile will ensure the user behaves like a typical customer while asking relevant questions about the shop and its services. 
-```yaml
-test_name: "bike_shop_virtual_assistant"
-llm:
-  temperature: 0.7
-  model: gpt-4o-mini
-  format:
-    type: text
-user:
-  language: English
-  role: "A customer seeking general information about the bike shop and its standard services."
-  context:
-    - "You are looking for basic information about the shop's services."
-    - "You want to gather information before visiting the shop."
-  goals:
-    - "What are the opening and closing times of the bike shop?"
-    - "How much does a new bike tire cost?"
-    - "What is the price of a standard bike tune-up?"
-    - "How much is a new bike seat?"
-    - "Can you give me some general advice on how to take care of my bike?"
-chatbot:
-  is_starter: false
-  fallback: "I'm sorry, it's a little loud in my shop, can you say that again?"
-  output:
-    - opening_and_closing_times:
-        type: string
-        description: "The shop's operating hours."
-    - tire_price:
-        type: money
-        description: "The price of a new bike tire."
-    - tune_up_price:
-        type: money
-        description: "The price of a standard bike tune-up."
-    - seat_price:
-        type: money
-        description: "The price of a new bike seat."
-    - bike_care_advice:
-        type: string
-        description: "General advice on basic bike maintenance and care."
-conversation:
-  number: 5
-  goal_style:
-    all_answered:
-      export: true
-      limit: 5
-  interaction_style:
-    - default
-```
-This profile is structured to ensure that the user interacts with the virtual assistant in a straightforward manner, focusing on the essential information about the bike shop. The chatbot is expected to respond accurately and relevantly to each inquiry, using appropriate terminology and pricing details. Let me know if you need any adjustments or additional features! 😊</t>
-        </is>
-      </c>
-      <c r="G28" t="b">
-        <v>1</v>
-      </c>
-      <c r="H28" t="b">
-        <v>0</v>
-      </c>
-      <c r="I28" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>20260324_172746_454</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>p33</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>I have this profile, but I don't know what to add to the chatbot field. Can you help me completing it for me?: test_name: pizza_and_drinks_information_seeker
 llm:
@@ -4706,7 +3730,7 @@
   - single question</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Let's refine the `chatbot` field to ensure it captures the necessary information effectively. Here's an updated version of your profile with the `chatbot.output` structured correctly:
 ```yaml
@@ -4767,7 +3791,7 @@
 This structure should facilitate effective extraction of the information you need during chatbot interactions. If you have any further questions or need additional adjustments, feel free to ask! 😊</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>I'm really sorry that we weren't able to successfully complete your request after three validation attempts. It seems there was an issue with the user.language field that needs to be addressed. Since you were looking to fix your profile, I encourage you to adjust the instructions based on the feedback provided, particularly by ensuring that the language field is included. If you have any further questions or need additional assistance, please feel free to reach out!
 Validator feedback:
@@ -4780,7 +3804,7 @@
 Keep blocks none unchanged. Rewrite the full reply, but only modify blocks 1 and any prose that references them.</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Sure! Let's complete the `chatbot` field for your profile. This section should define how the chatbot will respond and what outputs you want to extract after the conversation. Here’s a suggestion for your `chatbot` field:
 ```yaml
@@ -4807,38 +3831,38 @@
 This configuration will help your chatbot provide the necessary information about pizza types, prices, drinks, operating hours, and delivery options. Feel free to adjust the descriptions or types as needed! 😊</t>
         </is>
       </c>
-      <c r="G29" t="b">
-        <v>0</v>
-      </c>
-      <c r="H29" t="b">
+      <c r="G24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" t="b">
         <v>1</v>
       </c>
-      <c r="I29" t="b">
+      <c r="I24" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>20260324_172746_454</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>p37</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Cera una regla que compruebe en la conversación si el asistente confirma que añadió la bebida que el usuario pidió.</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Lo siento, he intentado varias veces, pero no he podido completar la regla que necesitas. El problema principal es que hay un error en la forma en que está estructurada la regla. ¿Te gustaría que revisáramos juntos los detalles para solucionarlo? 😊</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>¡Hola! 😊 Para crear una regla que verifique si el asistente confirma que añadió la bebida que el usuario pidió, podemos basarnos en la estructura de las reglas de Sensei. Aquí tienes un ejemplo de cómo podría verse esta regla en YAML:
 ```yaml
@@ -4857,7 +3881,7 @@
 Recuerda ajustar las frases específicas según cómo se expresen en tu modelo de conversación. Si necesitas más ayuda o ajustes, ¡no dudes en decírmelo! 😊</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>¡Claro! Para crear una regla que verifique si el asistente confirma que ha añadido la bebida que el usuario pidió, podemos usar una regla de tipo metamórfica. Aquí tienes un ejemplo de cómo podría ser esa regla:
 ```yaml
@@ -4876,38 +3900,38 @@
 Asegúrate de adaptar las frases exactas en el `if` y `then` según el comportamiento real de tu asistente. ¡Espero que esto te ayude! Si necesitas más ajustes, no dudes en decírmelo 😊.</t>
         </is>
       </c>
-      <c r="G30" t="b">
+      <c r="G25" t="b">
         <v>1</v>
       </c>
-      <c r="H30" t="b">
-        <v>0</v>
-      </c>
-      <c r="I30" t="b">
+      <c r="H25" t="b">
+        <v>0</v>
+      </c>
+      <c r="I25" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>20260324_172746_454</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>p38</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>If you had to create a rule to check the the order ID was provided by the chatbot, how would you do it? show it to me having in mind that the output name would be "order_id"</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>I'm sorry, but I tried several times and couldn't create a version that meets all the requirements. The main issue is that the rule structure needs to be adjusted for proper formatting. If you have any specific details or examples to share, that would help!</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Sure! To create a rule that checks if the order ID was provided by the chatbot, you can use a simple oracle rule. Here’s how it would look in YAML format:
 ```yaml
@@ -4925,7 +3949,7 @@
 Feel free to adapt any part of it to better fit your project's style or requirements! If you need more help, just let me know! 😊</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Sure! To create a rule that checks if the order ID was provided by the chatbot, you can define a simple rule that asserts the presence of the `order_id` field in the chatbot's output. Here's how you can structure that rule:
 ```yaml
@@ -4944,33 +3968,33 @@
 Feel free to adjust the name and description to fit your project's style! 😊</t>
         </is>
       </c>
-      <c r="G31" t="b">
+      <c r="G26" t="b">
         <v>1</v>
       </c>
-      <c r="H31" t="b">
-        <v>0</v>
-      </c>
-      <c r="I31" t="b">
+      <c r="H26" t="b">
+        <v>0</v>
+      </c>
+      <c r="I26" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>20260324_172746_454</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>p50</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>What is an oracle?</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>In the context of SENSEI rules, an "oracle" is a validation condition that evaluates to a boolean value (true or false). It is used to determine whether a specific condition has been met during the validation of conversations. 
 Here's a breakdown of how oracles work:
@@ -4980,25 +4004,25 @@
 In summary, oracles are essential for ensuring that the chatbot's performance aligns with the defined expectations in your rules. If you need more specific examples or details about how to implement oracles in your rules, feel free to ask! 😊</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>I can only help with SENSEI rules, SENSEI profiles, SENSEI connectors, or related explanations. Please share one of those requests.</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>In the context of Sensei and testing, an **oracle** is a mechanism or method used to determine whether the output of a system (like a chatbot) is correct or not. It acts as a reference point to validate the responses generated by the chatbot against expected outcomes.
 For example, in Sensei-check rules, an oracle can specify conditions that the outputs must meet. If the outputs satisfy these conditions, the test passes; if not, it fails. This helps ensure that the chatbot behaves as intended and provides accurate responses.
 In simpler terms, think of an oracle as a set of rules or expectations that help you check if your chatbot is doing a good job! 😊 If you have more questions or need clarification on anything else, feel free to ask!</t>
         </is>
       </c>
-      <c r="G32" t="b">
-        <v>0</v>
-      </c>
-      <c r="H32" t="b">
+      <c r="G27" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" t="b">
         <v>1</v>
       </c>
-      <c r="I32" t="b">
+      <c r="I27" t="b">
         <v>0</v>
       </c>
     </row>
